--- a/tc45.xlsx
+++ b/tc45.xlsx
@@ -425,27 +425,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>As a user</t>
+          <t>"IssueID": "US_402"</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I want to upload files in supported formats</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>So that the system can extract the content Supported File Types: .txt .csv .xlsx .json .xml .docx Acceptance Criteria: User should be able to upload supported file formats. System should validate the uploaded file. System should extract structured and unstructured content. System should generate a valid Excel (.xlsx) file. Excel file should contain: Bold headers Wrapped text Auto-adjusted column widths Proper alignment Borders System should upload generated Excel file to GitHub. System should return: GitHub File URL Raw Download URL GitHub Commit URL Extraction Summary System should return proper error messages for failures. Business Rules: Only supported file formats are allowed. GitHub token must be valid. Existing GitHub files should be updated if already present. Dependencies: GitHub API Excel generation library File parsing logic Assumptions: User provides valid GitHub repository details. Uploaded files are accessible during execution. Expected Result: The uploaded file content is successfully converted into a professionally formatted Excel file and stored in the specified GitHub repository.</t>
+          <t>"Description": "As a registered customer }</t>
         </is>
       </c>
     </row>
